--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_m_saldomigr_a_2021.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_m_saldomigr_a_2021.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:21</t>
+    <t xml:space="preserve">2026-09-24 01:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -717,10 +717,10 @@
         <v>11</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.1</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="15">
@@ -734,7 +734,7 @@
         <v>-0.03</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="16">
@@ -748,7 +748,7 @@
         <v>-0.11</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="17">
@@ -759,10 +759,10 @@
         <v>11</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18">
@@ -815,10 +815,10 @@
         <v>28</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.18</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22">
@@ -832,7 +832,7 @@
         <v>-0.19</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="23">
@@ -846,7 +846,7 @@
         <v>-0.11</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24">
@@ -857,10 +857,10 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="25">
@@ -874,7 +874,7 @@
         <v>0.18</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="26">
@@ -888,7 +888,7 @@
         <v>0.25</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_m_saldomigr_a_2021.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_m_saldomigr_a_2021.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:11</t>
+    <t xml:space="preserve">2026-10-01 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_m_saldomigr_a_2021.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_nacional_correl_matriz_m_saldomigr_a_2021.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:05</t>
+    <t xml:space="preserve">2026-10-05 19:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
